--- a/config/endless_tower_scene.xlsx
+++ b/config/endless_tower_scene.xlsx
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>第1ステージ</t>
+          <t>第一关卡</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>第2ステージ</t>
+          <t>第二关卡</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>第3ステージ</t>
+          <t>第三关卡</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>第4ステージ</t>
+          <t>第四关卡</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>第5ステージ</t>
+          <t>第五关卡</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="AI9" s="8" t="inlineStr">
         <is>
-          <t>敵の攻撃が一定の確率で火傷効果あり(解除可能)。</t>
+          <t>敌人的攻击有一定概率会有烧伤效果（可以解除）。</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>第6ステージ</t>
+          <t>第六关卡</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>第7ステージ</t>
+          <t>第七关卡</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>第8ステージ</t>
+          <t>第八关卡</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>第9ステージ</t>
+          <t>第九关卡</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>第10ステージ</t>
+          <t>第10关卡</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="AI14" s="8" t="inlineStr">
         <is>
-          <t>敵全員の特攻・物攻が上昇する。</t>
+          <t>全体敌人的特攻、物攻上升。</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>第11ステージ</t>
+          <t>第11关卡</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>第12ステージ</t>
+          <t>第12关卡</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>第13ステージ</t>
+          <t>第13关卡</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>第14ステージ</t>
+          <t>第14关卡</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>第15ステージ</t>
+          <t>第15关卡</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="AI19" s="8" t="inlineStr">
         <is>
-          <t>敵が攻撃時に一定の確率で速度を減少させる。</t>
+          <t>敌人攻击时会有一定概率减少速度。</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>第16ステージ</t>
+          <t>第16关卡</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>第17ステージ</t>
+          <t>第17关卡</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>第18ステージ</t>
+          <t>第18关卡</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>第19ステージ</t>
+          <t>第19关卡</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>第20ステージ</t>
+          <t>第20关卡</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="AI24" s="8" t="inlineStr">
         <is>
-          <t>敵全員の制御率UP、敵のシールドは制御解除の効果あり。</t>
+          <t>全体敌人的控制率UP，敌人的护盾有控制解除的效果。</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>第21ステージ</t>
+          <t>第21关卡</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>第22ステージ</t>
+          <t>第22关卡</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>第23ステージ</t>
+          <t>第23关卡</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>第24ステージ</t>
+          <t>第24关卡</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>第25ステージ</t>
+          <t>第25关卡</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="AI29" s="8" t="inlineStr">
         <is>
-          <t>敵が攻撃前に覚醒値を回復(光輪持ちの敵を撃破→覚醒値回復を制限)。</t>
+          <t>在攻击前回复敌人的觉醒值（击破持有光环的敌人→限制觉醒值回复）。</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>第26ステージ</t>
+          <t>第26关卡</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>第27ステージ</t>
+          <t>第27关卡</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>第28ステージ</t>
+          <t>第28关卡</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>第29ステージ</t>
+          <t>第29关卡</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>第30ステージ</t>
+          <t>第30关卡</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="AI34" s="8" t="inlineStr">
         <is>
-          <t>光輪は数ターンで消え、撃破時に味方全体にダメージUP付与。</t>
+          <t>光轮数回合后消失，击破时对全体伙伴增加伤害。</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>第31ステージ</t>
+          <t>第31关卡</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>第32ステージ</t>
+          <t>第32关卡</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>第33ステージ</t>
+          <t>第33关卡</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>第34ステージ</t>
+          <t>第34关卡</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>第35ステージ</t>
+          <t>第35关卡</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="AI39" s="8" t="inlineStr">
         <is>
-          <t>敵全体の会心率UP、光輪持ち撃破で効果解除。</t>
+          <t>提高全体敌人的暴击率，用光环击破解除效果。</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>第36ステージ</t>
+          <t>第36关卡</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>第37ステージ</t>
+          <t>第37关卡</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>第38ステージ</t>
+          <t>第38关卡</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>第39ステージ</t>
+          <t>第39关卡</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>第40ステージ</t>
+          <t>第40关卡</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="AI44" s="8" t="inlineStr">
         <is>
-          <t>敵全体に反射効果あり、光輪持ち撃破で吸血効果獲得。</t>
+          <t>所有敌人都有反射效果，光轮击破后获得吸血效果。</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>第41ステージ</t>
+          <t>第41关卡</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>第42ステージ</t>
+          <t>第42关卡</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>第43ステージ</t>
+          <t>第43关卡</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>第44ステージ</t>
+          <t>第44关卡</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>第45ステージ</t>
+          <t>第45关卡</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="AI49" s="8" t="inlineStr">
         <is>
-          <t>敵全体の制御率UP、光輪持ち撃破で味方の制御耐性UP。</t>
+          <t>敌人全体的控制率提高，用光环击破我方的控制耐性提高。</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>第46ステージ</t>
+          <t>第46关卡</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>第47ステージ</t>
+          <t>第47关卡</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7078,7 +7078,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>第48ステージ</t>
+          <t>第48关卡</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>第49ステージ</t>
+          <t>第49关卡</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>第50ステージ</t>
+          <t>第50关卡</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="AI54" s="8" t="inlineStr">
         <is>
-          <t>前列は防御力が高く、後列は低い。</t>
+          <t>前排防御力高，后排防御力低。</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>第51ステージ</t>
+          <t>第51关卡</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>第52ステージ</t>
+          <t>第52关卡</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>第53ステージ</t>
+          <t>第53关卡</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>第54ステージ</t>
+          <t>第54关卡</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>第55ステージ</t>
+          <t>第55关卡</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="AI59" s="8" t="inlineStr">
         <is>
-          <t>ランダムで1体の物防が大幅に上昇。</t>
+          <t>随机1只物防大幅上升。</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>第56ステージ</t>
+          <t>第56关卡</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>第57ステージ</t>
+          <t>第57关卡</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>第58ステージ</t>
+          <t>第58关卡</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>第59ステージ</t>
+          <t>第59关卡</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>第60ステージ</t>
+          <t>第60关卡</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="AI64" s="8" t="inlineStr">
         <is>
-          <t>敵全体の制御率が上昇、光輪持ち撃破で味方の制御耐性UP。</t>
+          <t>敌人全体的控制率上升，用光环击破我方的控制耐性提高。</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>第61ステージ</t>
+          <t>第61关卡</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>第62ステージ</t>
+          <t>第62关卡</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>第63ステージ</t>
+          <t>第63关卡</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>第64ステージ</t>
+          <t>第64关卡</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>第65ステージ</t>
+          <t>第65关卡</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="AI69" s="8" t="inlineStr">
         <is>
-          <t>敵の攻撃に確率で中毒効果あり、光輪持ち撃破で味方が回復。</t>
+          <t>敌人的攻击有机率有中毒效果，有光环击破能让我方回复。</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>第66ステージ</t>
+          <t>第66关卡</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>第67ステージ</t>
+          <t>第67关卡</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>第68ステージ</t>
+          <t>第68关卡</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -9567,7 +9567,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>第69ステージ</t>
+          <t>第69关卡</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -9680,7 +9680,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>第70ステージ</t>
+          <t>第70关卡</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="AI74" s="8" t="inlineStr">
         <is>
-          <t>光輪持ちの敵が撃破されると、範囲ダメージが発生。</t>
+          <t>持有光轮的敌人被击破时，会产生范围伤害。</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>第71ステージ</t>
+          <t>第71关卡</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>第72ステージ</t>
+          <t>第72关卡</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>第73ステージ</t>
+          <t>第73关卡</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>第74ステージ</t>
+          <t>第74关卡</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>第75ステージ</t>
+          <t>第75关卡</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="AI79" s="10" t="inlineStr">
         <is>
-          <t>敵全体の会心率UP、光輪持ち撃破で解除。</t>
+          <t>敌人全体的暴击率提高，用光环击破解除。</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>第76ステージ</t>
+          <t>第76关卡</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -10529,7 +10529,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>第77ステージ</t>
+          <t>第77关卡</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>第78ステージ</t>
+          <t>第78关卡</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -10755,7 +10755,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>第79ステージ</t>
+          <t>第79关卡</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>第80ステージ</t>
+          <t>第80关卡</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="AI84" s="8" t="inlineStr">
         <is>
-          <t>敵全体が確率で覚醒値を吸収、通常攻撃/スキルダメージUP。</t>
+          <t>全体敌人有概率吸收觉醒值，普通攻击/技能伤害UP。</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>第81ステージ</t>
+          <t>第81关卡</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>第82ステージ</t>
+          <t>第82关卡</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>第83ステージ</t>
+          <t>第83关卡</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -11349,7 +11349,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>第84ステージ</t>
+          <t>第84关卡</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>第85ステージ</t>
+          <t>第85关卡</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -11572,7 +11572,7 @@
       </c>
       <c r="AI89" s="8" t="inlineStr">
         <is>
-          <t>敵全員の物防/特防が上昇する。</t>
+          <t>全体敌人的物防/特防上升。</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>第86ステージ</t>
+          <t>第86关卡</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>第87ステージ</t>
+          <t>第87关卡</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>第88ステージ</t>
+          <t>第88关卡</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>第89ステージ</t>
+          <t>第89关卡</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>第90ステージ</t>
+          <t>第90关卡</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="AI94" s="8" t="inlineStr">
         <is>
-          <t>敵攻撃に確率で中毒効果あり、光輪持ち撃破で味方HP回復。</t>
+          <t>对敌人攻击有机率有中毒效果，光轮击破后我方HP回复。</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>第91ステージ</t>
+          <t>第91关卡</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>第92ステージ</t>
+          <t>第92关卡</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -12424,7 +12424,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>第93ステージ</t>
+          <t>第93关卡</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>第94ステージ</t>
+          <t>第94关卡</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>第95ステージ</t>
+          <t>第95关卡</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -12760,7 +12760,7 @@
       </c>
       <c r="AI99" s="8" t="inlineStr">
         <is>
-          <t>ランダムの1体の特殊防御が大幅に上昇する。</t>
+          <t>随机的1只特殊防御大幅上升。</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>第96ステージ</t>
+          <t>第96关卡</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -12905,7 +12905,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>第97ステージ</t>
+          <t>第97关卡</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -13018,7 +13018,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>第98ステージ</t>
+          <t>第98关卡</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>第99ステージ</t>
+          <t>第99关卡</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>第100ステージ</t>
+          <t>第100关卡</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="AI104" s="8" t="inlineStr">
         <is>
-          <t>敵全体が受ける特殊ダメージが減少、物理ダメージ上昇。</t>
+          <t>全体敌人受到的特殊伤害减少，物理伤害上升。</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>第101ステージ</t>
+          <t>第101关卡</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -13499,7 +13499,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>第102ステージ</t>
+          <t>第102关卡</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>第103ステージ</t>
+          <t>第103关卡</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>第104ステージ</t>
+          <t>第104关卡</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>第105ステージ</t>
+          <t>第105关卡</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="AI109" s="8" t="inlineStr">
         <is>
-          <t>敵のボスはどうやら眠っているようだ。</t>
+          <t>敌人的头头好像睡着了。</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>第106ステージ</t>
+          <t>第106关卡</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -14093,7 +14093,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>第107ステージ</t>
+          <t>第107关卡</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -14206,7 +14206,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>第108ステージ</t>
+          <t>第108关卡</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -14319,7 +14319,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>第109ステージ</t>
+          <t>第109关卡</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -14432,7 +14432,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>第110ステージ</t>
+          <t>第110关卡</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="AI114" s="8" t="inlineStr">
         <is>
-          <t>敵全体が受ける物理ダメージ減少、特殊ダメージ上昇。</t>
+          <t>全体敌人受到的物理伤害减少，特殊伤害上升。</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>第111ステージ</t>
+          <t>第111关卡</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -14687,7 +14687,7 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>第112ステージ</t>
+          <t>第112关卡</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -14800,7 +14800,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>第113ステージ</t>
+          <t>第113关卡</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -14913,7 +14913,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>第114ステージ</t>
+          <t>第114关卡</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>第115ステージ</t>
+          <t>第115关卡</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="AI119" s="8" t="inlineStr">
         <is>
-          <t>味方が禁錮されるのは、光輪と関係があるようだ。</t>
+          <t>伙伴被禁锢，似乎与光环有关。</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
@@ -15168,7 +15168,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>第116ステージ</t>
+          <t>第116关卡</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>第117ステージ</t>
+          <t>第117关卡</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>第118ステージ</t>
+          <t>第118关卡</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>第119ステージ</t>
+          <t>第119关卡</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>第120ステージ</t>
+          <t>第120关卡</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="AI124" s="8" t="inlineStr">
         <is>
-          <t>味方全体の物理/特殊攻撃UP、光輪撃破で物理/特殊防御UP。</t>
+          <t>我方全体物理/特殊攻击UP、光轮击破物理/特殊防御UP。</t>
         </is>
       </c>
       <c r="AJ124" t="inlineStr">
@@ -15762,7 +15762,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>第121ステージ</t>
+          <t>第121关卡</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -15875,7 +15875,7 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>第122ステージ</t>
+          <t>第122关卡</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -15988,7 +15988,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>第123ステージ</t>
+          <t>第123关卡</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -16101,7 +16101,7 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>第124ステージ</t>
+          <t>第124关卡</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>第125ステージ</t>
+          <t>第125关卡</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="AI129" s="8" t="inlineStr">
         <is>
-          <t>光輪は2回の攻撃を無効化し、ダメージを受けない。</t>
+          <t>光轮可以使2次攻击无效，不会受到伤害。</t>
         </is>
       </c>
       <c r="AJ129" t="inlineStr">
@@ -16356,7 +16356,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>第126ステージ</t>
+          <t>第126关卡</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>第127ステージ</t>
+          <t>第127关卡</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -16582,7 +16582,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>第128ステージ</t>
+          <t>第128关卡</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -16695,7 +16695,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>第129ステージ</t>
+          <t>第129关卡</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>第130ステージ</t>
+          <t>第130关卡</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -16918,7 +16918,7 @@
       </c>
       <c r="AI134" s="8" t="inlineStr">
         <is>
-          <t>ボスは他の敵から復活効果を獲得する。</t>
+          <t>boss从其他敌人身上获得复活效果。</t>
         </is>
       </c>
       <c r="AJ134" t="inlineStr">
@@ -16950,7 +16950,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>第131ステージ</t>
+          <t>第131关卡</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -17063,7 +17063,7 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>第132ステージ</t>
+          <t>第132关卡</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -17176,7 +17176,7 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>第133ステージ</t>
+          <t>第133关卡</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -17289,7 +17289,7 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>第134ステージ</t>
+          <t>第134关卡</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>第135ステージ</t>
+          <t>第135关卡</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -17512,7 +17512,7 @@
       </c>
       <c r="AI139" s="8" t="inlineStr">
         <is>
-          <t>味方は登場時に重傷、光輪撃破でHP回復。</t>
+          <t>我方登场时受重伤，光环击破回复HP。</t>
         </is>
       </c>
       <c r="AJ139" t="inlineStr">
@@ -17544,7 +17544,7 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>第136ステージ</t>
+          <t>第136关卡</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -17657,7 +17657,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>第137ステージ</t>
+          <t>第137关卡</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -17770,7 +17770,7 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>第138ステージ</t>
+          <t>第138关卡</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -17883,7 +17883,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>第139ステージ</t>
+          <t>第139关卡</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -17996,7 +17996,7 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>第140ステージ</t>
+          <t>第140关卡</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -18106,7 +18106,7 @@
       </c>
       <c r="AI144" s="8" t="inlineStr">
         <is>
-          <t>敵全体の制御率UP、光輪持ち撃破で解除。</t>
+          <t>敌人全体的控制率提高，用光环击破解除。</t>
         </is>
       </c>
       <c r="AJ144" t="inlineStr">
@@ -18138,7 +18138,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>第141ステージ</t>
+          <t>第141关卡</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -18251,7 +18251,7 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>第142ステージ</t>
+          <t>第142关卡</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -18364,7 +18364,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>第143ステージ</t>
+          <t>第143关卡</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -18477,7 +18477,7 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>第144ステージ</t>
+          <t>第144关卡</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -18590,7 +18590,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>第145ステージ</t>
+          <t>第145关卡</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -18700,7 +18700,7 @@
       </c>
       <c r="AI149" s="8" t="inlineStr">
         <is>
-          <t>雷属性の敵が継続的に金属性の敵をチャージする。</t>
+          <t>雷属性的敌人持续给金属属性的敌人充电。</t>
         </is>
       </c>
       <c r="AJ149" t="inlineStr">
@@ -18732,7 +18732,7 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>第146ステージ</t>
+          <t>第146关卡</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -18845,7 +18845,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>第147ステージ</t>
+          <t>第147关卡</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -18958,7 +18958,7 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>第148ステージ</t>
+          <t>第148关卡</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -19071,7 +19071,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>第149ステージ</t>
+          <t>第149关卡</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -19184,7 +19184,7 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>第150ステージ</t>
+          <t>第150关卡</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -19294,7 +19294,7 @@
       </c>
       <c r="AI154" s="8" t="inlineStr">
         <is>
-          <t>味方全体の物理/特殊防御が登場時に低下、光輪持ち撃破で解除。</t>
+          <t>我方全体的物理/特殊防御登场时下降，用光环击破解除。</t>
         </is>
       </c>
       <c r="AJ154" t="inlineStr">
@@ -19326,7 +19326,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>第151ステージ</t>
+          <t>第151关卡</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -19439,7 +19439,7 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>第152ステージ</t>
+          <t>第152关卡</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -19552,7 +19552,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>第153ステージ</t>
+          <t>第153关卡</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>第154ステージ</t>
+          <t>第154关卡</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>第155ステージ</t>
+          <t>第155关卡</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -19888,7 +19888,7 @@
       </c>
       <c r="AI159" s="8" t="inlineStr">
         <is>
-          <t>味方全体の速度と制御率が低下、光輪持ち撃破で解除。</t>
+          <t>我方全体的速度和控制率下降，用光环击破解除。</t>
         </is>
       </c>
       <c r="AJ159" t="inlineStr">
@@ -19920,7 +19920,7 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>第156ステージ</t>
+          <t>第156关卡</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -20033,7 +20033,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>第157ステージ</t>
+          <t>第157关卡</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -20146,7 +20146,7 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>第158ステージ</t>
+          <t>第158关卡</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -20259,7 +20259,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>第159ステージ</t>
+          <t>第159关卡</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -20372,7 +20372,7 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>第160ステージ</t>
+          <t>第160关卡</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -20482,7 +20482,7 @@
       </c>
       <c r="AI164" s="8" t="inlineStr">
         <is>
-          <t>全体のスキルダメージUP、光輪撃破で覚醒値が減少。</t>
+          <t>全体技能伤害提高，光环击破觉醒值减少。</t>
         </is>
       </c>
       <c r="AJ164" t="inlineStr">
@@ -20514,7 +20514,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>第161ステージ</t>
+          <t>第161关卡</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -20627,7 +20627,7 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>第162ステージ</t>
+          <t>第162关卡</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>第163ステージ</t>
+          <t>第163关卡</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>第164ステージ</t>
+          <t>第164关卡</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -20966,7 +20966,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>第165ステージ</t>
+          <t>第165关卡</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -21076,7 +21076,7 @@
       </c>
       <c r="AI169" s="8" t="inlineStr">
         <is>
-          <t>光輪を攻撃すると後列の敵の攻撃上昇、前列撃破で解除。</t>
+          <t>光环攻击后后排敌人的攻击上升，击破前排解除。</t>
         </is>
       </c>
       <c r="AJ169" t="inlineStr">
@@ -21108,7 +21108,7 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>第166ステージ</t>
+          <t>第166关卡</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -21221,7 +21221,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>第167ステージ</t>
+          <t>第167关卡</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -21334,7 +21334,7 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>第168ステージ</t>
+          <t>第168关卡</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>第169ステージ</t>
+          <t>第169关卡</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -21560,7 +21560,7 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>第170ステージ</t>
+          <t>第170关卡</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -21670,7 +21670,7 @@
       </c>
       <c r="AI174" s="8" t="inlineStr">
         <is>
-          <t>各ターン終了後、光輪キャラはボスのHPを回復させる。</t>
+          <t>每回合结束后，光轮角色会回复boss的生命值。</t>
         </is>
       </c>
       <c r="AJ174" t="inlineStr">
@@ -21702,7 +21702,7 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>第171ステージ</t>
+          <t>第171关卡</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -21815,7 +21815,7 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>第172ステージ</t>
+          <t>第172章</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -21928,7 +21928,7 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>第173ステージ</t>
+          <t>第173关卡</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -22041,7 +22041,7 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>第174ステージ</t>
+          <t>第174关卡</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -22154,7 +22154,7 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>第175ステージ</t>
+          <t>第175关卡</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -22264,7 +22264,7 @@
       </c>
       <c r="AI179" s="8" t="inlineStr">
         <is>
-          <t>敵全体の防御UP、光輪撃破で効果リセット。</t>
+          <t>全体敌人的防御UP，光轮击破效果复位。</t>
         </is>
       </c>
       <c r="AJ179" t="inlineStr">
@@ -22296,7 +22296,7 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>第176ステージ</t>
+          <t>第176关卡</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -22409,7 +22409,7 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>第177ステージ</t>
+          <t>第177章</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -22522,7 +22522,7 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>第178ステージ</t>
+          <t>第178关卡</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -22635,7 +22635,7 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>第179ステージ</t>
+          <t>第179关卡</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -22748,7 +22748,7 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>第180ステージ</t>
+          <t>第180关卡</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -22858,7 +22858,7 @@
       </c>
       <c r="AI184" s="6" t="inlineStr">
         <is>
-          <t>敵擬態状態で戦闘に参加する。</t>
+          <t>以敌拟态状态参加战斗。</t>
         </is>
       </c>
       <c r="AJ184" t="inlineStr">
@@ -22890,7 +22890,7 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>第181ステージ</t>
+          <t>第181关卡</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -23003,7 +23003,7 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>第182ステージ</t>
+          <t>第182章</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -23116,7 +23116,7 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>第183ステージ</t>
+          <t>第183关卡</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -23229,7 +23229,7 @@
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>第184ステージ</t>
+          <t>第184关卡</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -23342,7 +23342,7 @@
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>第185ステージ</t>
+          <t>第185关卡</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -23452,7 +23452,7 @@
       </c>
       <c r="AI189" s="8" t="inlineStr">
         <is>
-          <t>ボスを起こした仲間は離魂状態（攻撃UP/敵味方を区分しない）</t>
+          <t>触发boss的伙伴处于离魂状态（攻击UP/不分敌我）</t>
         </is>
       </c>
       <c r="AJ189" t="inlineStr">
@@ -23484,7 +23484,7 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>第186ステージ</t>
+          <t>第186关卡</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -23597,7 +23597,7 @@
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>第187ステージ</t>
+          <t>第187章</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -23710,7 +23710,7 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>第188ステージ</t>
+          <t>第188期</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -23823,7 +23823,7 @@
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>第189ステージ</t>
+          <t>第189关卡</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -23936,7 +23936,7 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>第190ステージ</t>
+          <t>第190关卡</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -24046,7 +24046,7 @@
       </c>
       <c r="AI194" s="8" t="inlineStr">
         <is>
-          <t>光輪持ちは反撃＆特攻・物攻減少を付与(数ターンで消失)。</t>
+          <t>光环持有者可以给予反击、特攻、物攻减少（数回合后消失）。</t>
         </is>
       </c>
       <c r="AJ194" t="inlineStr">
@@ -24078,7 +24078,7 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>第191ステージ</t>
+          <t>第191关卡</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -24191,7 +24191,7 @@
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>第192ステージ</t>
+          <t>第192关卡</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>第193ステージ</t>
+          <t>第193关卡</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -24417,7 +24417,7 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>第194ステージ</t>
+          <t>第194关卡</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -24530,7 +24530,7 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>第195ステージ</t>
+          <t>第195关卡</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -24640,7 +24640,7 @@
       </c>
       <c r="AI199" s="8" t="inlineStr">
         <is>
-          <t>ターン開始時、光輪持ちが生存中は敵が攻撃力が最も高い味方を攻撃。</t>
+          <t>回合开始时，光环持有者生存时，敌人会攻击攻击力最高的伙伴。</t>
         </is>
       </c>
       <c r="AJ199" t="inlineStr">
@@ -24672,7 +24672,7 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>第196ステージ</t>
+          <t>第196章</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -24785,7 +24785,7 @@
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>第197ステージ</t>
+          <t>第197关卡</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -24898,7 +24898,7 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>第198ステージ</t>
+          <t>第198关卡</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -25011,7 +25011,7 @@
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>第199ステージ</t>
+          <t>第199关卡</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -25124,7 +25124,7 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>第200ステージ</t>
+          <t>第200关卡</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AI204" s="8" t="inlineStr">
         <is>
-          <t>ターン開始時、敵全体の回避率UP、光輪持ち撃破で解除。</t>
+          <t>回合开始时，敌人全体回避率UP，光环击破解除。</t>
         </is>
       </c>
       <c r="AJ204" t="inlineStr">
@@ -25266,7 +25266,7 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>第201ステージ</t>
+          <t>第201关卡</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -25379,7 +25379,7 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>第202ステージ</t>
+          <t>第202关卡</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -25492,7 +25492,7 @@
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>第203ステージ</t>
+          <t>第203关卡</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -25605,7 +25605,7 @@
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>第204ステージ</t>
+          <t>第204关卡</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -25718,7 +25718,7 @@
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>第205ステージ</t>
+          <t>第205关卡</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -25828,7 +25828,7 @@
       </c>
       <c r="AI209" s="6" t="inlineStr">
         <is>
-          <t>敵復讐で、自分を倒した仲間に擬態する。</t>
+          <t>拟态成敌人复仇时打倒自己的伙伴。</t>
         </is>
       </c>
       <c r="AJ209" t="inlineStr">
@@ -25860,7 +25860,7 @@
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>第206ステージ</t>
+          <t>第206关卡</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -25973,7 +25973,7 @@
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>第207ステージ</t>
+          <t>第207关卡</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -26086,7 +26086,7 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>第208ステージ</t>
+          <t>第208关卡</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -26199,7 +26199,7 @@
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>第209ステージ</t>
+          <t>第209关卡</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -26312,7 +26312,7 @@
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>第210ステージ</t>
+          <t>第210关卡</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -26422,7 +26422,7 @@
       </c>
       <c r="AI214" s="8" t="inlineStr">
         <is>
-          <t>全体の覚醒値を封印、光輪持ち撃破で解除。</t>
+          <t>封印所有觉醒值，用光环击破解除。</t>
         </is>
       </c>
       <c r="AJ214" t="inlineStr">
@@ -26454,7 +26454,7 @@
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>第211ステージ</t>
+          <t>第211关卡</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -26567,7 +26567,7 @@
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>第212ステージ</t>
+          <t>第212关卡</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -26680,7 +26680,7 @@
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>第213ステージ</t>
+          <t>第213关卡</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -26793,7 +26793,7 @@
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>第214ステージ</t>
+          <t>第214关卡</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -26906,7 +26906,7 @@
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>第215ステージ</t>
+          <t>第215关卡</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -27016,7 +27016,7 @@
       </c>
       <c r="AI219" s="8" t="inlineStr">
         <is>
-          <t>全体の覚醒回復量が減少、光輪持ち撃破で解除。</t>
+          <t>全体觉醒回复量减少，用光环击破解除。</t>
         </is>
       </c>
       <c r="AJ219" t="inlineStr">
@@ -27048,7 +27048,7 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>第216ステージ</t>
+          <t>第216关卡</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>第217ステージ</t>
+          <t>第217关卡</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -27274,7 +27274,7 @@
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>第218ステージ</t>
+          <t>第218关卡</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -27387,7 +27387,7 @@
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>第219ステージ</t>
+          <t>第219关卡</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -27500,7 +27500,7 @@
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>第220ステージ</t>
+          <t>第220关卡</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -27610,7 +27610,7 @@
       </c>
       <c r="AI224" s="8" t="inlineStr">
         <is>
-          <t>全員の敵の覚醒値回復速度が上昇する。</t>
+          <t>全体敌人的觉醒值回复速度上升。</t>
         </is>
       </c>
       <c r="AJ224" t="inlineStr">
@@ -27642,7 +27642,7 @@
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>第221ステージ</t>
+          <t>第221关卡</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -27755,7 +27755,7 @@
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>第222ステージ</t>
+          <t>第222关卡</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -27868,7 +27868,7 @@
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>第223ステージ</t>
+          <t>第223关卡</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -27981,7 +27981,7 @@
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>第224ステージ</t>
+          <t>第224关卡</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -28094,7 +28094,7 @@
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>第225ステージ</t>
+          <t>第225关卡</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -28204,7 +28204,7 @@
       </c>
       <c r="AI229" s="8" t="inlineStr">
         <is>
-          <t>ターンごとに全員の最大HP減少、光輪持ち撃破で解除。</t>
+          <t>每回合全员最大HP减少，光环击破解除。</t>
         </is>
       </c>
       <c r="AJ229" t="inlineStr">
@@ -28236,7 +28236,7 @@
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>第226ステージ</t>
+          <t>第226关卡</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>第227ステージ</t>
+          <t>第227章</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -28462,7 +28462,7 @@
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>第228ステージ</t>
+          <t>第228关卡</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -28575,7 +28575,7 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>第229ステージ</t>
+          <t>第229关卡</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -28688,7 +28688,7 @@
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>第230ステージ</t>
+          <t>第230关卡</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -28798,7 +28798,7 @@
       </c>
       <c r="AI234" s="8" t="inlineStr">
         <is>
-          <t>敵全体のスキルダメージUP、光輪持ち撃破で解除。</t>
+          <t>敌人全体的技能伤害提高，用光环击破解除。</t>
         </is>
       </c>
       <c r="AJ234" t="inlineStr">
@@ -28830,7 +28830,7 @@
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>第231ステージ</t>
+          <t>第231关卡</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -28943,7 +28943,7 @@
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>第232ステージ</t>
+          <t>第232关卡</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -29056,7 +29056,7 @@
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>第233ステージ</t>
+          <t>第233关卡</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -29169,7 +29169,7 @@
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>第234ステージ</t>
+          <t>第234关卡</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -29282,7 +29282,7 @@
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>第235ステージ</t>
+          <t>第235关卡</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -29392,7 +29392,7 @@
       </c>
       <c r="AI239" s="8" t="inlineStr">
         <is>
-          <t>敵全体の回復量UP、光輪持ち撃破で解除。</t>
+          <t>敌人全体回复量提升，光环击破解除。</t>
         </is>
       </c>
       <c r="AJ239" t="inlineStr">
@@ -29424,7 +29424,7 @@
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>第236ステージ</t>
+          <t>第236关卡</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -29537,7 +29537,7 @@
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>第237ステージ</t>
+          <t>第237关卡</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -29650,7 +29650,7 @@
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>第238ステージ</t>
+          <t>第238关卡</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -29763,7 +29763,7 @@
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>第239ステージ</t>
+          <t>第239关卡</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -29876,7 +29876,7 @@
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>第240ステージ</t>
+          <t>第240关卡</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -29986,7 +29986,7 @@
       </c>
       <c r="AI244" s="8" t="inlineStr">
         <is>
-          <t>敵はHPが低いほど与ダメージ上昇、光輪持ち撃破で解除。</t>
+          <t>敌人的生命值越低，给予伤害就越高，用光环击破解除。</t>
         </is>
       </c>
       <c r="AJ244" t="inlineStr">
@@ -30018,7 +30018,7 @@
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>第241ステージ</t>
+          <t>第241关卡</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -30131,7 +30131,7 @@
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>第242ステージ</t>
+          <t>第242关卡</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -30244,7 +30244,7 @@
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>第243ステージ</t>
+          <t>第243章</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -30357,7 +30357,7 @@
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>第244ステージ</t>
+          <t>第244关卡</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -30470,7 +30470,7 @@
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>第245ステージ</t>
+          <t>第245关卡</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -30580,7 +30580,7 @@
       </c>
       <c r="AI249" s="8" t="inlineStr">
         <is>
-          <t>光輪持ち撃破で他の敵の覚醒値が上昇。</t>
+          <t>光环击破能提升其他敌人的觉醒值。</t>
         </is>
       </c>
       <c r="AJ249" t="inlineStr">
@@ -30612,7 +30612,7 @@
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>第246ステージ</t>
+          <t>第246关卡</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -30725,7 +30725,7 @@
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>第247ステージ</t>
+          <t>第247章</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -30838,7 +30838,7 @@
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>第248ステージ</t>
+          <t>第248关卡</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -30951,7 +30951,7 @@
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>第249ステージ</t>
+          <t>第249关卡</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -31064,7 +31064,7 @@
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>第250ステージ</t>
+          <t>第250关卡</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -31174,7 +31174,7 @@
       </c>
       <c r="AI254" s="8" t="inlineStr">
         <is>
-          <t>敵全体の制御率上昇、光輪持ち撃破で解除。</t>
+          <t>敌人全体的控制率上升，用光环击破解除。</t>
         </is>
       </c>
       <c r="AJ254" t="inlineStr">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>第251ステージ</t>
+          <t>第251关卡</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -31319,7 +31319,7 @@
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>第252ステージ</t>
+          <t>第252章</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -31432,7 +31432,7 @@
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>第253ステージ</t>
+          <t>第253关卡</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -31545,7 +31545,7 @@
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>第254ステージ</t>
+          <t>第254关卡</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -31658,7 +31658,7 @@
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>第255ステージ</t>
+          <t>第255章</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -31768,7 +31768,7 @@
       </c>
       <c r="AI259" s="8" t="inlineStr">
         <is>
-          <t>数ターン後、敵側に全体シールドが付与される。</t>
+          <t>几个回合后，敌方将被赋予全盾。</t>
         </is>
       </c>
       <c r="AJ259" t="inlineStr">
@@ -31800,7 +31800,7 @@
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>第256ステージ</t>
+          <t>第256关卡</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -31913,7 +31913,7 @@
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>第257ステージ</t>
+          <t>第257章</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -32026,7 +32026,7 @@
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>第258ステージ</t>
+          <t>第258关卡</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -32139,7 +32139,7 @@
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>第259ステージ</t>
+          <t>第259章</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -32252,7 +32252,7 @@
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>第260ステージ</t>
+          <t>第260关卡</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -32362,7 +32362,7 @@
       </c>
       <c r="AI264" s="8" t="inlineStr">
         <is>
-          <t>敵全体のダメージ反射率上昇、光輪持ち撃破で解除。</t>
+          <t>敌人全体的伤害反射率上升，用光环击破解除。</t>
         </is>
       </c>
       <c r="AJ264" t="inlineStr">
@@ -32394,7 +32394,7 @@
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>第261ステージ</t>
+          <t>第261关卡</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -32507,7 +32507,7 @@
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>第262ステージ</t>
+          <t>第262关卡</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -32620,7 +32620,7 @@
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>第263ステージ</t>
+          <t>第263关卡</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -32733,7 +32733,7 @@
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>第264ステージ</t>
+          <t>第264关卡</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -32846,7 +32846,7 @@
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>第265ステージ</t>
+          <t>第265关卡</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -32956,7 +32956,7 @@
       </c>
       <c r="AI269" s="8" t="inlineStr">
         <is>
-          <t>敵全員が撃破される度に全体に自爆ダメージを与える。</t>
+          <t>敌人全体被击破时给予全体自爆伤害。</t>
         </is>
       </c>
       <c r="AJ269" t="inlineStr">
@@ -32988,7 +32988,7 @@
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>第266ステージ</t>
+          <t>第266关卡</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -33101,7 +33101,7 @@
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>第267ステージ</t>
+          <t>第267关卡</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -33214,7 +33214,7 @@
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>第268ステージ</t>
+          <t>第268章</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -33327,7 +33327,7 @@
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>第269ステージ</t>
+          <t>第269章</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -33440,7 +33440,7 @@
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>第270ステージ</t>
+          <t>第270章</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -33550,7 +33550,7 @@
       </c>
       <c r="AI274" s="8" t="inlineStr">
         <is>
-          <t>敵全員が擬態し、全てを破壊する。</t>
+          <t>所有敌人拟态并摧毁一切。</t>
         </is>
       </c>
       <c r="AJ274" t="inlineStr">
@@ -33582,7 +33582,7 @@
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>第271ステージ</t>
+          <t>第271关卡</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -33695,7 +33695,7 @@
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>第272ステージ</t>
+          <t>第272关卡</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -33808,7 +33808,7 @@
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>第273ステージ</t>
+          <t>第273关卡</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -33921,7 +33921,7 @@
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>第274ステージ</t>
+          <t>第274关卡</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>第275ステージ</t>
+          <t>第275关卡</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -34144,7 +34144,7 @@
       </c>
       <c r="AI279" s="6" t="inlineStr">
         <is>
-          <t>敵が擬態</t>
+          <t>敌人拟态</t>
         </is>
       </c>
       <c r="AJ279" t="inlineStr">
@@ -34176,7 +34176,7 @@
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>第276ステージ</t>
+          <t>第276章</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -34289,7 +34289,7 @@
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>第277ステージ</t>
+          <t>第277关卡</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -34402,7 +34402,7 @@
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>第278ステージ</t>
+          <t>第278期</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -34515,7 +34515,7 @@
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>第279ステージ</t>
+          <t>第279章</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -34628,7 +34628,7 @@
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>第280ステージ</t>
+          <t>第280关卡</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -34738,7 +34738,7 @@
       </c>
       <c r="AI284" s="8" t="inlineStr">
         <is>
-          <t>偶数ターンで擬態</t>
+          <t>拟态在偶数回合</t>
         </is>
       </c>
       <c r="AJ284" t="inlineStr">
@@ -34770,7 +34770,7 @@
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>第281ステージ</t>
+          <t>第281章</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -34883,7 +34883,7 @@
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>第282ステージ</t>
+          <t>第282关卡</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -34996,7 +34996,7 @@
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>第283ステージ</t>
+          <t>第283关卡</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -35109,7 +35109,7 @@
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>第284ステージ</t>
+          <t>第284关卡</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -35222,7 +35222,7 @@
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>第285ステージ</t>
+          <t>第285章</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -35332,7 +35332,7 @@
       </c>
       <c r="AI289" s="8" t="inlineStr">
         <is>
-          <t>第5ターンで仲間全員が隠密を獲得</t>
+          <t>第5回合所有伙伴都获得了隐密</t>
         </is>
       </c>
       <c r="AJ289" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>第286ステージ</t>
+          <t>第286关卡</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -35477,7 +35477,7 @@
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>第287ステージ</t>
+          <t>第287章</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -35590,7 +35590,7 @@
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>第288ステージ</t>
+          <t>第288关卡</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -35703,7 +35703,7 @@
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>第289ステージ</t>
+          <t>第289关卡</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -35816,7 +35816,7 @@
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>第290ステージ</t>
+          <t>第290期</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -35926,7 +35926,7 @@
       </c>
       <c r="AI294" s="8" t="inlineStr">
         <is>
-          <t>第6ターン開始後から必ず回避する。</t>
+          <t>从第6回合开始后一定回避。</t>
         </is>
       </c>
       <c r="AJ294" t="inlineStr">
@@ -35958,7 +35958,7 @@
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>第291ステージ</t>
+          <t>第291关卡</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -36071,7 +36071,7 @@
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>第292ステージ</t>
+          <t>第292关卡</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -36184,7 +36184,7 @@
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>第293ステージ</t>
+          <t>第293关卡</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -36297,7 +36297,7 @@
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>第294ステージ</t>
+          <t>第294期</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>第295ステージ</t>
+          <t>第295章</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -36520,7 +36520,7 @@
       </c>
       <c r="AI299" s="8" t="inlineStr">
         <is>
-          <t>味方全体の防御が減少、光輪持ち撃破で解除。</t>
+          <t>我方全体防御减少，用光环击破解除。</t>
         </is>
       </c>
       <c r="AJ299" t="inlineStr">
@@ -36552,7 +36552,7 @@
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>第296ステージ</t>
+          <t>第296关卡</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -36665,7 +36665,7 @@
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>第297ステージ</t>
+          <t>第297关卡</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -36778,7 +36778,7 @@
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>第298ステージ</t>
+          <t>第298关卡</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -36891,7 +36891,7 @@
       </c>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t>第299ステージ</t>
+          <t>第299关卡</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -37004,7 +37004,7 @@
       </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>第300ステージ</t>
+          <t>第300关卡</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -37114,7 +37114,7 @@
       </c>
       <c r="AI304" s="8" t="inlineStr">
         <is>
-          <t>光輪持ちは攻撃される度にHP回復＆攻撃力上昇</t>
+          <t>光环持有者每次受到攻击都会回复生命值并提升攻击力</t>
         </is>
       </c>
       <c r="AJ304" t="inlineStr">
@@ -37146,7 +37146,7 @@
       </c>
       <c r="B305" s="3" t="inlineStr">
         <is>
-          <t>第301ステージ</t>
+          <t>第301关卡</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -37264,7 +37264,7 @@
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>第302ステージ</t>
+          <t>第302关卡</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -37382,7 +37382,7 @@
       </c>
       <c r="B307" s="3" t="inlineStr">
         <is>
-          <t>第303ステージ</t>
+          <t>第303关卡</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -37500,7 +37500,7 @@
       </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>第304ステージ</t>
+          <t>第304关卡</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -37618,7 +37618,7 @@
       </c>
       <c r="B309" s="3" t="inlineStr">
         <is>
-          <t>第305ステージ</t>
+          <t>第305关卡</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -37733,7 +37733,7 @@
       </c>
       <c r="AI309" s="8" t="inlineStr">
         <is>
-          <t>光輪持ちの敵がいる間、受ける火傷ダメージが50%上昇。</t>
+          <t>有光环的敌人时，受到的烧伤伤害提升50%。</t>
         </is>
       </c>
       <c r="AJ309" t="inlineStr">
@@ -37755,7 +37755,7 @@
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>第306ステージ</t>
+          <t>第306关卡</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -37873,7 +37873,7 @@
       </c>
       <c r="B311" s="3" t="inlineStr">
         <is>
-          <t>第307ステージ</t>
+          <t>第307关卡</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -37991,7 +37991,7 @@
       </c>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>第308ステージ</t>
+          <t>第308关卡</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="B313" s="3" t="inlineStr">
         <is>
-          <t>第309ステージ</t>
+          <t>第309关卡</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -38227,7 +38227,7 @@
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>第310ステージ</t>
+          <t>第310关卡</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -38342,7 +38342,7 @@
       </c>
       <c r="AI314" s="8" t="inlineStr">
         <is>
-          <t>攻撃時、対象の攻撃力が10%減少(共闘・連撃・挑戦含む)</t>
+          <t>攻击时，对象的攻击力减少10%（包含共斗、连击、挑战）</t>
         </is>
       </c>
       <c r="AJ314" t="inlineStr">
@@ -38364,7 +38364,7 @@
       </c>
       <c r="B315" s="3" t="inlineStr">
         <is>
-          <t>第311ステージ</t>
+          <t>第311关卡</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -38482,7 +38482,7 @@
       </c>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>第312ステージ</t>
+          <t>第312关卡</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -38600,7 +38600,7 @@
       </c>
       <c r="B317" s="3" t="inlineStr">
         <is>
-          <t>第313ステージ</t>
+          <t>第313关卡</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -38718,7 +38718,7 @@
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>第314ステージ</t>
+          <t>第314关卡</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -38836,7 +38836,7 @@
       </c>
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>第315ステージ</t>
+          <t>第315关卡</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -38951,7 +38951,7 @@
       </c>
       <c r="AI319" s="8" t="inlineStr">
         <is>
-          <t>光輪持ちがいる間、全体の反射ダメージ+30%</t>
+          <t>光环持有者存在时，整体反射伤害+30%</t>
         </is>
       </c>
       <c r="AJ319" t="inlineStr">
@@ -38973,7 +38973,7 @@
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>第316ステージ</t>
+          <t>第316关卡</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -39091,7 +39091,7 @@
       </c>
       <c r="B321" s="3" t="inlineStr">
         <is>
-          <t>第317ステージ</t>
+          <t>第317章</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -39209,7 +39209,7 @@
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>第318ステージ</t>
+          <t>第318关卡</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -39327,7 +39327,7 @@
       </c>
       <c r="B323" s="3" t="inlineStr">
         <is>
-          <t>第319ステージ</t>
+          <t>第319关卡</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -39445,7 +39445,7 @@
       </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>第320ステージ</t>
+          <t>第320关卡</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -39560,7 +39560,7 @@
       </c>
       <c r="AI324" s="7" t="inlineStr">
         <is>
-          <t>敵覚醒値値が300回復する。</t>
+          <t>敌人觉醒值回复300。</t>
         </is>
       </c>
       <c r="AJ324" t="inlineStr">
@@ -39582,7 +39582,7 @@
       </c>
       <c r="B325" s="3" t="inlineStr">
         <is>
-          <t>第321ステージ</t>
+          <t>第321关卡</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -39700,7 +39700,7 @@
       </c>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>第322ステージ</t>
+          <t>第322关卡</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -39818,7 +39818,7 @@
       </c>
       <c r="B327" s="3" t="inlineStr">
         <is>
-          <t>第323ステージ</t>
+          <t>第323关卡</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>第324ステージ</t>
+          <t>第324关卡</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -40054,7 +40054,7 @@
       </c>
       <c r="B329" s="3" t="inlineStr">
         <is>
-          <t>第325ステージ</t>
+          <t>第325章</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -40169,7 +40169,7 @@
       </c>
       <c r="AI329" s="8" t="inlineStr">
         <is>
-          <t>光輪持ちがいる間、撃破される時に特攻の追加ダメージを付与。</t>
+          <t>光环持有者存在期间，被击破时给予特攻的追加伤害。</t>
         </is>
       </c>
       <c r="AJ329" t="inlineStr">
@@ -40191,7 +40191,7 @@
       </c>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>第326ステージ</t>
+          <t>第326关卡</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -40309,7 +40309,7 @@
       </c>
       <c r="B331" s="3" t="inlineStr">
         <is>
-          <t>第327ステージ</t>
+          <t>第327关卡</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -40427,7 +40427,7 @@
       </c>
       <c r="B332" s="3" t="inlineStr">
         <is>
-          <t>第328ステージ</t>
+          <t>第328关卡</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -40545,7 +40545,7 @@
       </c>
       <c r="B333" s="3" t="inlineStr">
         <is>
-          <t>第329ステージ</t>
+          <t>第329关卡</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -40663,7 +40663,7 @@
       </c>
       <c r="B334" s="3" t="inlineStr">
         <is>
-          <t>第330ステージ</t>
+          <t>第330关卡</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -40778,7 +40778,7 @@
       </c>
       <c r="AI334" s="8" t="inlineStr">
         <is>
-          <t>光輪持ちがいる間、全員に中毒＆中毒状態に追加ダメージ。</t>
+          <t>光环持有者在场时，全员中毒&amp;中毒状态追加伤害。</t>
         </is>
       </c>
       <c r="AJ334" t="inlineStr">
@@ -40800,7 +40800,7 @@
       </c>
       <c r="B335" s="3" t="inlineStr">
         <is>
-          <t>第331ステージ</t>
+          <t>第331关卡</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -40918,7 +40918,7 @@
       </c>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>第332ステージ</t>
+          <t>第332关卡</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -41036,7 +41036,7 @@
       </c>
       <c r="B337" s="3" t="inlineStr">
         <is>
-          <t>第333ステージ</t>
+          <t>第333关卡</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -41154,7 +41154,7 @@
       </c>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>第334ステージ</t>
+          <t>第334关卡</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -41272,7 +41272,7 @@
       </c>
       <c r="B339" s="3" t="inlineStr">
         <is>
-          <t>第335ステージ</t>
+          <t>第335关卡</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -41387,7 +41387,7 @@
       </c>
       <c r="AI339" s="8" t="inlineStr">
         <is>
-          <t>光輪持ちがいる間、ターン開始時にランダム1～3体に凍結付与。</t>
+          <t>光环持有者存在期间，回合开始时随机冻结1 ~ 3个。</t>
         </is>
       </c>
       <c r="AJ339" t="inlineStr">
@@ -41409,7 +41409,7 @@
       </c>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>第336ステージ</t>
+          <t>第336关卡</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -41527,7 +41527,7 @@
       </c>
       <c r="B341" s="3" t="inlineStr">
         <is>
-          <t>第337ステージ</t>
+          <t>第337关卡</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -41645,7 +41645,7 @@
       </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>第338ステージ</t>
+          <t>第338关卡</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="B343" s="3" t="inlineStr">
         <is>
-          <t>第339ステージ</t>
+          <t>第339关卡</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -41881,7 +41881,7 @@
       </c>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>第340ステージ</t>
+          <t>第340关卡</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -41996,7 +41996,7 @@
       </c>
       <c r="AI344" s="8" t="inlineStr">
         <is>
-          <t>光輪持ちいる間、全体の会心率＆会心ダメージが30%上昇。</t>
+          <t>有光轮时，全体暴击率和暴击伤害上升30%。</t>
         </is>
       </c>
       <c r="AJ344" t="inlineStr">
@@ -42018,7 +42018,7 @@
       </c>
       <c r="B345" s="3" t="inlineStr">
         <is>
-          <t>第341ステージ</t>
+          <t>第341关卡</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -42136,7 +42136,7 @@
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>第342ステージ</t>
+          <t>第342关卡</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -42254,7 +42254,7 @@
       </c>
       <c r="B347" s="3" t="inlineStr">
         <is>
-          <t>第343ステージ</t>
+          <t>第343关卡</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -42372,7 +42372,7 @@
       </c>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>第344ステージ</t>
+          <t>第344关卡</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -42490,7 +42490,7 @@
       </c>
       <c r="B349" s="3" t="inlineStr">
         <is>
-          <t>第345ステージ</t>
+          <t>第345关卡</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -42605,7 +42605,7 @@
       </c>
       <c r="AI349" s="8" t="inlineStr">
         <is>
-          <t>光輪持ちがいる間、ターン終了後に覚醒値を300回復。</t>
+          <t>光环持有者在场时，回合结束后觉醒值回复300。</t>
         </is>
       </c>
       <c r="AJ349" t="inlineStr">
@@ -42627,7 +42627,7 @@
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>第346ステージ</t>
+          <t>第346关卡</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -42745,7 +42745,7 @@
       </c>
       <c r="B351" s="3" t="inlineStr">
         <is>
-          <t>第347ステージ</t>
+          <t>第347关卡</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -42863,7 +42863,7 @@
       </c>
       <c r="B352" s="3" t="inlineStr">
         <is>
-          <t>第348ステージ</t>
+          <t>第348关卡</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="B353" s="3" t="inlineStr">
         <is>
-          <t>第349ステージ</t>
+          <t>第349章</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -43099,7 +43099,7 @@
       </c>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>第350ステージ</t>
+          <t>第350关卡</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -43214,7 +43214,7 @@
       </c>
       <c r="AI354" s="8" t="inlineStr">
         <is>
-          <t>光輪持ちがいる間、覚醒値の回復速度が40%減少。</t>
+          <t>光环持有者存在时，觉醒值回复速度减少40%。</t>
         </is>
       </c>
       <c r="AJ354" t="inlineStr">
@@ -43236,7 +43236,7 @@
       </c>
       <c r="B355" s="3" t="inlineStr">
         <is>
-          <t>第351ステージ</t>
+          <t>第351关卡</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -43354,7 +43354,7 @@
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>第352ステージ</t>
+          <t>第352关卡</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -43472,7 +43472,7 @@
       </c>
       <c r="B357" s="3" t="inlineStr">
         <is>
-          <t>第353ステージ</t>
+          <t>第353章</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="B358" s="3" t="inlineStr">
         <is>
-          <t>第354ステージ</t>
+          <t>第354关卡</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -43708,7 +43708,7 @@
       </c>
       <c r="B359" s="3" t="inlineStr">
         <is>
-          <t>第355ステージ</t>
+          <t>第355关卡</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -43823,7 +43823,7 @@
       </c>
       <c r="AI359" s="8" t="inlineStr">
         <is>
-          <t>敵が倒れた後、その仲間は毎回行動する前に憤怒でいっぱいになる。</t>
+          <t>敌人倒下后，他的伙伴每次行动前都会充满愤怒。</t>
         </is>
       </c>
       <c r="AJ359" t="inlineStr">
@@ -43845,7 +43845,7 @@
       </c>
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>第356ステージ</t>
+          <t>第356关卡</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -43963,7 +43963,7 @@
       </c>
       <c r="B361" s="3" t="inlineStr">
         <is>
-          <t>第357ステージ</t>
+          <t>第357章</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -44081,7 +44081,7 @@
       </c>
       <c r="B362" s="3" t="inlineStr">
         <is>
-          <t>第358ステージ</t>
+          <t>第358章</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -44199,7 +44199,7 @@
       </c>
       <c r="B363" s="3" t="inlineStr">
         <is>
-          <t>第359ステージ</t>
+          <t>第359章</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -44317,7 +44317,7 @@
       </c>
       <c r="B364" s="3" t="inlineStr">
         <is>
-          <t>第360ステージ</t>
+          <t>第360关卡</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -44432,7 +44432,7 @@
       </c>
       <c r="AI364" s="8" t="inlineStr">
         <is>
-          <t>各ターンごとに敵全員に1段の鳳王火傷を付与。</t>
+          <t>各回合给予全体敌人1段凤王烧伤。</t>
         </is>
       </c>
       <c r="AJ364" t="inlineStr">
@@ -44454,7 +44454,7 @@
       </c>
       <c r="B365" s="3" t="inlineStr">
         <is>
-          <t>第361ステージ</t>
+          <t>第361关卡</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -44572,7 +44572,7 @@
       </c>
       <c r="B366" s="3" t="inlineStr">
         <is>
-          <t>第362ステージ</t>
+          <t>第362关卡</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -44690,7 +44690,7 @@
       </c>
       <c r="B367" s="3" t="inlineStr">
         <is>
-          <t>第363ステージ</t>
+          <t>第363关卡</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -44808,7 +44808,7 @@
       </c>
       <c r="B368" s="3" t="inlineStr">
         <is>
-          <t>第364ステージ</t>
+          <t>第364关卡</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -44926,7 +44926,7 @@
       </c>
       <c r="B369" s="3" t="inlineStr">
         <is>
-          <t>第365ステージ</t>
+          <t>第365关卡</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -45041,7 +45041,7 @@
       </c>
       <c r="AI369" s="8" t="inlineStr">
         <is>
-          <t>各ターンの開始時に、BOSSの確率でランダムな敵2体に熟睡を付与します。</t>
+          <t>各回合开始时，BOSS的概率随机给予2个敌人熟睡。</t>
         </is>
       </c>
       <c r="AJ369" t="inlineStr">
@@ -45063,7 +45063,7 @@
       </c>
       <c r="B370" s="3" t="inlineStr">
         <is>
-          <t>第366ステージ</t>
+          <t>第366章</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -45181,7 +45181,7 @@
       </c>
       <c r="B371" s="3" t="inlineStr">
         <is>
-          <t>第367ステージ</t>
+          <t>第367关卡</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -45299,7 +45299,7 @@
       </c>
       <c r="B372" s="3" t="inlineStr">
         <is>
-          <t>第368ステージ</t>
+          <t>第368关卡</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="B373" s="3" t="inlineStr">
         <is>
-          <t>第369ステージ</t>
+          <t>第369关卡</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -45535,7 +45535,7 @@
       </c>
       <c r="B374" s="3" t="inlineStr">
         <is>
-          <t>第370ステージ</t>
+          <t>第370关卡</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -45650,7 +45650,7 @@
       </c>
       <c r="AI374" s="8" t="inlineStr">
         <is>
-          <t>敵連撃効果を持ち(連続で同じ攻撃)、速度が50%上昇。</t>
+          <t>拥有敌人连击效果（连续攻击相同），速度上升50%。</t>
         </is>
       </c>
       <c r="AJ374" t="inlineStr">
@@ -45672,7 +45672,7 @@
       </c>
       <c r="B375" s="3" t="inlineStr">
         <is>
-          <t>第371ステージ</t>
+          <t>第371关卡</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -45790,7 +45790,7 @@
       </c>
       <c r="B376" s="3" t="inlineStr">
         <is>
-          <t>第372ステージ</t>
+          <t>第372关卡</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -45908,7 +45908,7 @@
       </c>
       <c r="B377" s="3" t="inlineStr">
         <is>
-          <t>第373ステージ</t>
+          <t>第373关卡</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -46026,7 +46026,7 @@
       </c>
       <c r="B378" s="3" t="inlineStr">
         <is>
-          <t>第374ステージ</t>
+          <t>第374关卡</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -46144,7 +46144,7 @@
       </c>
       <c r="B379" s="3" t="inlineStr">
         <is>
-          <t>第375ステージ</t>
+          <t>第375关卡</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -46259,7 +46259,7 @@
       </c>
       <c r="AI379" s="8" t="inlineStr">
         <is>
-          <t>各大回合の終了後、敵は全てのシールドを築きます。</t>
+          <t>每次大回合结束后，敌人将建立所有盾牌。</t>
         </is>
       </c>
       <c r="AJ379" t="inlineStr">
@@ -46281,7 +46281,7 @@
       </c>
       <c r="B380" s="3" t="inlineStr">
         <is>
-          <t>第376ステージ</t>
+          <t>第376号关卡</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -46399,7 +46399,7 @@
       </c>
       <c r="B381" s="3" t="inlineStr">
         <is>
-          <t>第377ステージ</t>
+          <t>第377关卡</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -46517,7 +46517,7 @@
       </c>
       <c r="B382" s="3" t="inlineStr">
         <is>
-          <t>第378ステージ</t>
+          <t>第378关卡</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -46635,7 +46635,7 @@
       </c>
       <c r="B383" s="3" t="inlineStr">
         <is>
-          <t>第379ステージ</t>
+          <t>第379关卡</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -46753,7 +46753,7 @@
       </c>
       <c r="B384" s="3" t="inlineStr">
         <is>
-          <t>第380ステージ</t>
+          <t>第380关卡</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -46868,7 +46868,7 @@
       </c>
       <c r="AI384" s="8" t="inlineStr">
         <is>
-          <t>スキル発動後、敵隠密化し、撃破成功でCT短縮。</t>
+          <t>技能发动后，敌人隐密化，击破成功后CT缩短。</t>
         </is>
       </c>
       <c r="AJ384" t="inlineStr">
@@ -46890,7 +46890,7 @@
       </c>
       <c r="B385" s="3" t="inlineStr">
         <is>
-          <t>第381ステージ</t>
+          <t>第381关卡</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -47008,7 +47008,7 @@
       </c>
       <c r="B386" s="3" t="inlineStr">
         <is>
-          <t>第382ステージ</t>
+          <t>第382关卡</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -47126,7 +47126,7 @@
       </c>
       <c r="B387" s="3" t="inlineStr">
         <is>
-          <t>第383ステージ</t>
+          <t>第383关卡</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -47244,7 +47244,7 @@
       </c>
       <c r="B388" s="3" t="inlineStr">
         <is>
-          <t>第384ステージ</t>
+          <t>第384章</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -47362,7 +47362,7 @@
       </c>
       <c r="B389" s="3" t="inlineStr">
         <is>
-          <t>第385ステージ</t>
+          <t>第385关卡</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -47477,7 +47477,7 @@
       </c>
       <c r="AI389" s="8" t="inlineStr">
         <is>
-          <t>敵は毎回アクティブスキルを受けると隠密状態に入り（怒りを回復しない）</t>
+          <t>敌人每次接受主动技能后进入隐密状态（不回复愤怒）</t>
         </is>
       </c>
       <c r="AJ389" t="inlineStr">
@@ -47499,7 +47499,7 @@
       </c>
       <c r="B390" s="3" t="inlineStr">
         <is>
-          <t>第386ステージ</t>
+          <t>第386关卡</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -47617,7 +47617,7 @@
       </c>
       <c r="B391" s="3" t="inlineStr">
         <is>
-          <t>第387ステージ</t>
+          <t>第387关卡</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -47735,7 +47735,7 @@
       </c>
       <c r="B392" s="3" t="inlineStr">
         <is>
-          <t>第388ステージ</t>
+          <t>第388关卡</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -47853,7 +47853,7 @@
       </c>
       <c r="B393" s="3" t="inlineStr">
         <is>
-          <t>第389ステージ</t>
+          <t>第389关卡</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -47971,7 +47971,7 @@
       </c>
       <c r="B394" s="3" t="inlineStr">
         <is>
-          <t>第390ステージ</t>
+          <t>第390关卡</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -48086,7 +48086,7 @@
       </c>
       <c r="AI394" s="8" t="inlineStr">
         <is>
-          <t>敵通常攻撃を受けると、相手に青焔灼焼と青焔ダメージを付与。</t>
+          <t>受到敌人普通攻击时，给予对手青火焰灼烧和青火焰伤害。</t>
         </is>
       </c>
       <c r="AJ394" t="inlineStr">
@@ -48108,7 +48108,7 @@
       </c>
       <c r="B395" s="3" t="inlineStr">
         <is>
-          <t>第391ステージ</t>
+          <t>第391章</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -48226,7 +48226,7 @@
       </c>
       <c r="B396" s="3" t="inlineStr">
         <is>
-          <t>第392ステージ</t>
+          <t>第392关卡</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -48344,7 +48344,7 @@
       </c>
       <c r="B397" s="3" t="inlineStr">
         <is>
-          <t>第393ステージ</t>
+          <t>第393关卡</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -48462,7 +48462,7 @@
       </c>
       <c r="B398" s="3" t="inlineStr">
         <is>
-          <t>第394ステージ</t>
+          <t>第394章</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -48580,7 +48580,7 @@
       </c>
       <c r="B399" s="3" t="inlineStr">
         <is>
-          <t>第395ステージ</t>
+          <t>第395章</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -48695,7 +48695,7 @@
       </c>
       <c r="AI399" s="8" t="inlineStr">
         <is>
-          <t>味方に草属性がいないと、敵全体が隠密化(5ターン持続)</t>
+          <t>我方没有草属性的话，敌人全体隐身化（持续5回合）</t>
         </is>
       </c>
       <c r="AJ399" t="inlineStr">
@@ -48717,7 +48717,7 @@
       </c>
       <c r="B400" s="3" t="inlineStr">
         <is>
-          <t>第396ステージ</t>
+          <t>第396关卡</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -48835,7 +48835,7 @@
       </c>
       <c r="B401" s="3" t="inlineStr">
         <is>
-          <t>第397ステージ</t>
+          <t>第397章</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -48953,7 +48953,7 @@
       </c>
       <c r="B402" s="3" t="inlineStr">
         <is>
-          <t>第398ステージ</t>
+          <t>第398关卡</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="B403" s="3" t="inlineStr">
         <is>
-          <t>第399ステージ</t>
+          <t>第399关卡</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -49189,7 +49189,7 @@
       </c>
       <c r="B404" s="3" t="inlineStr">
         <is>
-          <t>第400ステージ</t>
+          <t>第400关卡</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -49304,7 +49304,7 @@
       </c>
       <c r="AI404" s="8" t="inlineStr">
         <is>
-          <t>味方が撃破される度、敵の特防/特攻ダメージ減少+15%。</t>
+          <t>己方被击破时，敌方特防/特攻伤害减少+15%。</t>
         </is>
       </c>
       <c r="AJ404" t="inlineStr">
